--- a/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/04_Finanzierung_Sicherheiten/05_Sicherheitenregister_Bank.xlsx
+++ b/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/04_Finanzierung_Sicherheiten/05_Sicherheitenregister_Bank.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sicherheiten" sheetId="1" r:id="R0253efdb2c044569"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Freigaben" sheetId="2" r:id="R6d71bcad8b7e418c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sicherheiten" sheetId="1" r:id="Rf7839c0e5572445b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Freigaben" sheetId="2" r:id="Rc6def2eeb54b4f31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hauptschuldbezug" sheetId="3" r:id="R3f3ce36e0dc54ec9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -626,4 +627,133 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="45" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="4" t="str">
+        <x:v>Sicherheitenregister der Bank</x:v>
+      </x:c>
+      <x:c r="B1" s="4"/>
+      <x:c r="C1" s="4"/>
+      <x:c r="D1" s="4"/>
+      <x:c r="E1" s="4"/>
+      <x:c r="F1" s="4"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="4"/>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="8" t="str">
+        <x:v>Arbeitsstand aus den beigefügten Aktenstücken; offene Angaben bleiben offen und sind nicht als Nullwert zu behandeln.</x:v>
+      </x:c>
+      <x:c r="B3" s="8"/>
+      <x:c r="C3" s="8"/>
+      <x:c r="D3" s="8"/>
+      <x:c r="E3" s="8"/>
+      <x:c r="F3" s="8"/>
+    </x:row>
+    <x:row r="5" ht="36" customHeight="1">
+      <x:c r="A5" s="11" t="str">
+        <x:v>Sicherheit</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>Gesicherter Vertrag</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>Darlehenskonto</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>Höchstkapital</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>Saldo 22.10.2026</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="str">
+        <x:v>Freigabestatus</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="34" customHeight="1">
+      <x:c r="A6" s="14" t="str">
+        <x:v>Film- und Nutzungsrechte</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="str">
+        <x:v>KLP-2024-0418 + Nachtrag 10.01.2025</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="str">
+        <x:v>KD-2417-01</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="n">
+        <x:v>2270000</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="n">
+        <x:v>1476830.44</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="str">
+        <x:v>keine Freigabe</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="34" customHeight="1">
+      <x:c r="A7" s="15" t="str">
+        <x:v>Mastermedien und Geräte</x:v>
+      </x:c>
+      <x:c r="B7" s="15" t="str">
+        <x:v>KLP-2024-0418 + Einbeziehungsbestätigung 17.02.2026</x:v>
+      </x:c>
+      <x:c r="C7" s="15" t="str">
+        <x:v>KD-2417-01</x:v>
+      </x:c>
+      <x:c r="D7" s="15" t="n">
+        <x:v>2270000</x:v>
+      </x:c>
+      <x:c r="E7" s="15" t="n">
+        <x:v>1476830.44</x:v>
+      </x:c>
+      <x:c r="F7" s="15" t="str">
+        <x:v>keine Freigabe</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="34" customHeight="1">
+      <x:c r="A8" s="14" t="str">
+        <x:v>Lizenzforderungen</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>KLP-2024-0418 + Nachtrag 10.01.2025</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>KD-2417-01</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="n">
+        <x:v>2270000</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="n">
+        <x:v>1476830.44</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>keine Freigabe</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F2"/>
+    <x:mergeCell ref="A3:F3"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/04_Finanzierung_Sicherheiten/05_Sicherheitenregister_Bank.xlsx
+++ b/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/04_Finanzierung_Sicherheiten/05_Sicherheitenregister_Bank.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sicherheiten" sheetId="1" r:id="Rf7839c0e5572445b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Freigaben" sheetId="2" r:id="Rc6def2eeb54b4f31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hauptschuldbezug" sheetId="3" r:id="R3f3ce36e0dc54ec9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sicherheiten" sheetId="1" r:id="R6aeb567ae0144d0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Freigaben" sheetId="2" r:id="R3e2d9f7e7f834cc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hauptschuldbezug" sheetId="3" r:id="R2d3b1da2b1fc4952"/>
   </x:sheets>
 </x:workbook>
 </file>
